--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abinaya\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EB04A4D-D52D-44BB-BA63-E6C2037D08FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{640669B1-0FEF-45E4-A50C-161B85D37CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C34945A-6B99-4E78-BB48-B4E6A8DE307D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD671DBE-167B-400D-8495-9CF14C894D0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,82 +39,209 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Field Desc</t>
-  </si>
-  <si>
-    <t>Nationality</t>
-  </si>
-  <si>
-    <t>IN</t>
-  </si>
-  <si>
-    <t>Customer Nationality</t>
-  </si>
-  <si>
-    <t>OriginCountry</t>
-  </si>
-  <si>
-    <t>AE</t>
-  </si>
-  <si>
-    <t>Mailing Country</t>
-  </si>
-  <si>
-    <t>MultipleNationalityCntryCode1</t>
-  </si>
-  <si>
-    <t>UK</t>
-  </si>
-  <si>
-    <t>IInd Nationality If applicable</t>
-  </si>
-  <si>
-    <t>AccountClassification</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Hard coded</t>
-  </si>
-  <si>
-    <t>FATCAClassification</t>
-  </si>
-  <si>
-    <t>W8BenOrW9Status</t>
-  </si>
-  <si>
-    <t>USResident</t>
-  </si>
-  <si>
-    <t>Blank</t>
-  </si>
-  <si>
-    <t>FATCAGCApproval</t>
-  </si>
-  <si>
-    <t>NonUAEResident</t>
-  </si>
-  <si>
-    <t>VersionNumber</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>Finding</t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Current Status</t>
+  </si>
+  <si>
+    <t>F#1 – Broken Authentication</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Direct access to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>Menu.aspx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> allows bypassing the login page.</t>
+    </r>
+  </si>
+  <si>
+    <t>Fixed in UAT – Pending GIS validation.</t>
+  </si>
+  <si>
+    <t>F#2 – Sitewide Broken Authorization (Throttle)</t>
+  </si>
+  <si>
+    <t>Unauthorized users can access pages/functions by navigating directly to URLs and throttling the network connection.</t>
+  </si>
+  <si>
+    <r>
+      <t>Fixed in UAT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>WF_ApplicationDataEntry.aspx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>WF_CA.aspx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Pending GIS benchmarking. Once validated, the fix will be extended across the site.</t>
+    </r>
+  </si>
+  <si>
+    <t>F#4 – Storage of Password in a Reversible Format</t>
+  </si>
+  <si>
+    <t>Username/password and other sensitive credentials are stored in a reversible/Base64 format.</t>
+  </si>
+  <si>
+    <r>
+      <t>Implementation in progress</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Strong cryptographic encryption is being implemented.</t>
+    </r>
+  </si>
+  <si>
+    <t>F#5 – Sitewide SQL Injection</t>
+  </si>
+  <si>
+    <t>Multiple fields across the application are vulnerable to SQL injection involving both Oracle and MSSQL connections.</t>
+  </si>
+  <si>
+    <r>
+      <t>Partially implemented.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Fix completed for a few pages. Remaining pages are in progress. This is an extensive sitewide activity and requires significant implementation effort.</t>
+    </r>
+  </si>
+  <si>
+    <t>F#7 – Sitewide Improper Data Validation</t>
+  </si>
+  <si>
+    <t>Request parameters can be modified; sensitive information can be exposed; read-only records can potentially be modified and submitted to the database.</t>
+  </si>
+  <si>
+    <r>
+      <t>Solution under discussion/finalization.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sitewide implementation is extensive and will require significant effort.</t>
+    </r>
+  </si>
+  <si>
+    <t>F#8 – Unauthenticated Services</t>
+  </si>
+  <si>
+    <t>Generated PDF files have predictable filenames, and URLs can potentially be reused from another browser/user.</t>
+  </si>
+  <si>
+    <t>F#9 – Unauthorized User Can View Staff Salary</t>
+  </si>
+  <si>
+    <t>Unauthorized users can access sensitive salary information.</t>
+  </si>
+  <si>
+    <t>Implementation in progress.</t>
+  </si>
+  <si>
+    <t>F#14 – Potential Directory Traversal Attack</t>
+  </si>
+  <si>
+    <t>Potential directory traversal vulnerability identified.</t>
+  </si>
+  <si>
+    <t>Analysis in progress.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -127,6 +254,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -137,7 +270,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -171,13 +304,15 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,122 +646,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C468E12B-257C-4829-A977-C383EC1A13A6}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77816E65-480E-4B8E-A63E-D67697B320C9}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="48.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:3" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
+      <c r="A8" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abinaya\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{640669B1-0FEF-45E4-A50C-161B85D37CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F322909-EEB1-4FC8-8D20-037B2B144A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD671DBE-167B-400D-8495-9CF14C894D0F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DD671DBE-167B-400D-8495-9CF14C894D0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,31 +40,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>Finding</t>
-  </si>
-  <si>
-    <t>Observation</t>
-  </si>
-  <si>
-    <t>Current Status</t>
-  </si>
-  <si>
-    <t>F#1 – Broken Authentication</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>No. of Pages</t>
+  </si>
+  <si>
+    <t>Approach</t>
+  </si>
+  <si>
+    <t>Productivity</t>
+  </si>
+  <si>
+    <t>Estimated Effort</t>
+  </si>
+  <si>
+    <t>Normal pages – Authentication &amp; Authorization</t>
+  </si>
+  <si>
+    <t>~650</t>
+  </si>
+  <si>
+    <t>C# server-side authentication/authorization + JavaScript frame validation</t>
+  </si>
+  <si>
+    <t>30–50 pages/day</t>
+  </si>
+  <si>
+    <t>13–22 working days</t>
+  </si>
+  <si>
+    <t>Query String based pages</t>
+  </si>
+  <si>
+    <t>~50</t>
+  </si>
+  <si>
+    <t>Query String encryption + Username validation/authentication + page-level authorization</t>
+  </si>
+  <si>
+    <t>3–5 pages/day</t>
+  </si>
+  <si>
+    <t>10–17 working days</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Direct access to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>Menu.aspx</t>
+      <t>~700 pages</t>
     </r>
     <r>
       <rPr>
@@ -73,164 +101,157 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> allows bypassing the login page.</t>
+      <t>*</t>
     </r>
   </si>
   <si>
-    <t>Fixed in UAT – Pending GIS validation.</t>
-  </si>
-  <si>
-    <t>F#2 – Sitewide Broken Authorization (Throttle)</t>
-  </si>
-  <si>
-    <t>Unauthorized users can access pages/functions by navigating directly to URLs and throttling the network connection.</t>
-  </si>
-  <si>
-    <r>
-      <t>Fixed in UAT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>WF_ApplicationDataEntry.aspx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>WF_CA.aspx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Pending GIS benchmarking. Once validated, the fix will be extended across the site.</t>
-    </r>
-  </si>
-  <si>
-    <t>F#4 – Storage of Password in a Reversible Format</t>
-  </si>
-  <si>
-    <t>Username/password and other sensitive credentials are stored in a reversible/Base64 format.</t>
-  </si>
-  <si>
-    <r>
-      <t>Implementation in progress</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> – Strong cryptographic encryption is being implemented.</t>
-    </r>
-  </si>
-  <si>
-    <t>F#5 – Sitewide SQL Injection</t>
-  </si>
-  <si>
-    <t>Multiple fields across the application are vulnerable to SQL injection involving both Oracle and MSSQL connections.</t>
-  </si>
-  <si>
-    <r>
-      <t>Partially implemented.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Fix completed for a few pages. Remaining pages are in progress. This is an extensive sitewide activity and requires significant implementation effort.</t>
-    </r>
-  </si>
-  <si>
-    <t>F#7 – Sitewide Improper Data Validation</t>
-  </si>
-  <si>
-    <t>Request parameters can be modified; sensitive information can be exposed; read-only records can potentially be modified and submitted to the database.</t>
-  </si>
-  <si>
-    <r>
-      <t>Solution under discussion/finalization.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Sitewide implementation is extensive and will require significant effort.</t>
-    </r>
-  </si>
-  <si>
-    <t>F#8 – Unauthenticated Services</t>
-  </si>
-  <si>
-    <t>Generated PDF files have predictable filenames, and URLs can potentially be reused from another browser/user.</t>
-  </si>
-  <si>
-    <t>F#9 – Unauthorized User Can View Staff Salary</t>
-  </si>
-  <si>
-    <t>Unauthorized users can access sensitive salary information.</t>
-  </si>
-  <si>
-    <t>Implementation in progress.</t>
-  </si>
-  <si>
-    <t>F#14 – Potential Directory Traversal Attack</t>
-  </si>
-  <si>
-    <t>Potential directory traversal vulnerability identified.</t>
-  </si>
-  <si>
-    <t>Analysis in progress.</t>
+    <t>23–39 working days</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Approx. Pages</t>
+  </si>
+  <si>
+    <t>Effort Basis</t>
+  </si>
+  <si>
+    <t>Phase 1</t>
+  </si>
+  <si>
+    <t>Normal / non-workflow pages</t>
+  </si>
+  <si>
+    <t>~445</t>
+  </si>
+  <si>
+    <t>9–15 person-days</t>
+  </si>
+  <si>
+    <t>Phase 2</t>
+  </si>
+  <si>
+    <t>Workflow pages</t>
+  </si>
+  <si>
+    <t>~220</t>
+  </si>
+  <si>
+    <t>30–50 pages/day, with additional workflow validation</t>
+  </si>
+  <si>
+    <t>8–12 person-days</t>
+  </si>
+  <si>
+    <t>Query String pages</t>
+  </si>
+  <si>
+    <t>4 hours/page</t>
+  </si>
+  <si>
+    <t>25 person-days</t>
+  </si>
+  <si>
+    <t>~715</t>
+  </si>
+  <si>
+    <t>42–52 person-days</t>
+  </si>
+  <si>
+    <t>Implementation Approach</t>
+  </si>
+  <si>
+    <t>Productivity / Effort</t>
+  </si>
+  <si>
+    <t>All applicable pages excluding the 220 workflow pages</t>
+  </si>
+  <si>
+    <t>~495</t>
+  </si>
+  <si>
+    <t>Common C# authentication/authorization + JavaScript frame validation. Query String handling for applicable pages.</t>
+  </si>
+  <si>
+    <t>Normal: 30–50 pages/day; Query String: 4 hrs/page</t>
+  </si>
+  <si>
+    <t>~28–34 person-days</t>
+  </si>
+  <si>
+    <t>C# authentication/authorization + JavaScript frame validation, with page-specific validation based on workflow/navigation behaviour</t>
+  </si>
+  <si>
+    <t>~5–8 person-days</t>
+  </si>
+  <si>
+    <t>~33–42 person-days</t>
+  </si>
+  <si>
+    <t>Phase 1 will cover the non-workflow pages and applicable Query String-based pages.
+Activities include:
+Implement server-side C# authentication and authorization.
+Validate the logged-in user's identity/session.
+Prevent direct URL access without authentication.
+Implement JavaScript validation to ensure the page is loaded within the authorized HFLMS frame.
+Handle slow network/throttling scenarios so that unauthorized content/actions are not exposed while the page is loading.
+For applicable Query String pages:
+Encrypt Query String parameters.
+Pass the authenticated Username/UserID as part of the protected request.
+Decrypt and validate the request server-side.
+Authenticate the UserID against the current session/user.
+Prevent manipulation or reuse of another user's URL.
+Perform page-level functional/regression validation.
+Estimated effort: 30–35 person-days.</t>
+  </si>
+  <si>
+    <t>Phase 1 – ~445 Normal Pages
+Estimated effort: 9–15 person-days
+Implementation includes:
+Server-side C# authentication and authorization.
+Session/UserID validation.
+Prevention of direct URL access.
+JavaScript frame validation.
+Slow-network/throttling protection.
+Page-level implementation and validation.
+Regression testing of existing functionality.
+The productivity is estimated at 30–50 pages/day, since these pages use the common security mechanism.
+Phase 2 – ~270 Pages
+A. ~220 Workflow Pages
+Estimated effort: 8–12 person-days
+Although the common C# and JavaScript mechanism will be reused, additional effort is required for:
+Workflow-specific navigation validation.
+Page-to-page transition validation.
+Authentication/authorization checks across workflow journeys.
+Direct URL access validation.
+Slow-network/throttling scenarios.
+Regression testing of existing workflow functionality.
+The workflow pages are therefore handled separately to reduce the risk of impacting critical business journeys.
+B. ~50 Query String Pages
+Estimated effort: 25 person-days
+Calculation:
+50 pages × 4 hours/page = 200 hours = 25 person-days
+These pages require additional implementation because authorization is linked to the Query String.
+For each page:
+Encrypt the Query String.
+Include the authenticated Username/UserID in the protected request.
+Decrypt the Query String server-side.
+Validate the UserID against the current authenticated session.
+Validate that the Query String has not been modified.
+Prevent one user from using another user's URL/data.
+Validate existing functionality after encryption.
+Perform page-level testing.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,12 +274,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -302,8 +317,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -312,6 +336,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -647,106 +689,253 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77816E65-480E-4B8E-A63E-D67697B320C9}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="48.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D2" s="10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="E2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
+      <c r="B15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E651421A-F907-4951-A69B-ABADE1D73D0D}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
